--- a/feedback-reports/Front-end_Dev_with_React_and_GenAI_Advanced_Program.xlsx
+++ b/feedback-reports/Front-end_Dev_with_React_and_GenAI_Advanced_Program.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3042AF75-6E86-424F-8407-3C349A2A67E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="14_{3042AF75-6E86-424F-8407-3C349A2A67E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3AB3B84A-7847-4627-A5BA-D2B410734FBB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
   <si>
     <t>Program Name:</t>
   </si>
@@ -180,6 +180,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with:
@@ -191,6 +192,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Responsive Web Design &amp; User Experience
@@ -201,6 +203,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create visually appealing and responsive web interfaces by structuring content effectively and applying modern styling practices aligned with UI/UX principles.
@@ -212,6 +215,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Interactive Web Development &amp; API Integration
@@ -222,6 +226,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build dynamic, interactive web applications by handling user interactions and seamlessly connecting front-end interfaces with backend services through APIs.</t>
@@ -278,6 +283,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Replace with below:
@@ -289,6 +295,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Component-Based UI Development
@@ -299,6 +306,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build reusable and maintainable user interfaces using JSX, components, and props.
@@ -310,6 +318,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> State, Interactivity &amp; Data Handling
@@ -320,6 +329,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create dynamic apps by managing state, handling interactions, and integrating APIs with React hooks.
@@ -331,6 +341,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Scalable, Styled &amp; Tested Apps
@@ -341,6 +352,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Improve reliability with TypeScript, design responsive UIs using Material UI, and ensure quality through testing using Jest and RTL.</t>
@@ -382,6 +394,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Replace with below content:
@@ -393,6 +406,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Forms &amp; Navigation in React Applications
@@ -403,6 +417,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build and validate complex forms and enable seamless user journeys through efficient form handling and in-app routing.
@@ -414,6 +429,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Authentication, State Management &amp; Performance
@@ -424,6 +440,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Implement secure access control and manage application state effectively using Context API while optimizing performance for production-ready apps.</t>
@@ -537,6 +554,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Add with:
 • </t>
@@ -547,6 +565,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">SQL Querying &amp; Data Operations
 </t>
@@ -556,6 +575,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Build strong hands-on skills to retrieve, analyze, and manipulate data using SQL, enabling you to extract meaningful insights and work effectively with real-world datasets.
 • </t>
@@ -566,6 +586,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Database Design, Integrity &amp; Advanced Capabilities
 </t>
@@ -575,6 +596,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>Design structured databases using ER diagrams and define robust schemas while ensuring data consistency, and extend functionality through automation and support for modern data formats.</t>
     </r>
@@ -591,6 +613,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Add with : 
 1)</t>
@@ -601,6 +624,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Core Java Programming &amp; Problem Solving
 </t>
@@ -610,6 +634,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Apply Core Java fundamentals—variables, control flow, arrays, strings, recursion, and searching/sorting—to build efficient, program logic.
 2) </t>
@@ -620,6 +645,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Object-Oriented Application Development
 </t>
@@ -629,6 +655,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Apply object-oriented concepts and exception handling to design well-structured Java applications.</t>
     </r>
@@ -645,6 +672,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Add with :
@@ -656,6 +684,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Data Structures Implementation
@@ -666,6 +695,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Implement core data structures such as arrays, stacks, queues, linked lists, trees, and hash tables along with searching and sorting algorithms.
@@ -677,6 +707,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Algorithm Analysis and Optimization
@@ -687,6 +718,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Analyse time and space complexity and apply recursion and suitable data structures to solve performance-critical problems.</t>
@@ -704,6 +736,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add with:
@@ -715,6 +748,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Testing and Collections
@@ -725,6 +759,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Write unit tests and manage data using collections and generics for organized, reliable programs.
@@ -736,6 +771,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Modern Java Practices
@@ -746,6 +782,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply functional programming features to write concise, efficient code for data processing.</t>
@@ -781,6 +818,9 @@
 5. HostelBites Lite – Smart Mess Manager — Build a responsive React + TypeScript app using components, state, and hooks to manage meal preferences and demand insights.
 6. MovieMate – Personal Watchlist — Build a React SPA to explore, filter, and manage a personalized movie watchlist using routing, forms, global state, and performance optimizations.</t>
     </r>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -800,15 +840,18 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -816,29 +859,34 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -853,6 +901,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -904,7 +953,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -927,12 +976,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -968,6 +1028,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1282,6 +1348,7 @@
     <col min="5" max="5" width="40" style="2" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
     <col min="7" max="7" width="58.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1300,8 +1367,8 @@
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1315,11 +1382,11 @@
       <c r="D2" s="4"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1339,6 +1406,9 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1361,7 +1431,8 @@
       <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="8"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -1424,7 +1495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="179.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1443,7 +1514,7 @@
       <c r="F8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1990,12 +2061,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008081BF50E816F94B87E854E2907183B0" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6f57204d0cc9b1c65f7ab94eaa7dcc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b8ad293-1655-4b1e-95cd-578b981aff66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed196dee19b1527225c6137bc92e865" ns2:_="">
     <xsd:import namespace="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
@@ -2157,6 +2222,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2167,22 +2238,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2BB2AD3-7CBE-41F4-9CD2-29EEE306E664}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{730B4967-9014-486D-BC0B-FED06405060C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2200,6 +2255,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2BB2AD3-7CBE-41F4-9CD2-29EEE306E664}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30BD62A0-3FD1-4B18-9B85-9BA10240F7E5}">
   <ds:schemaRefs>

--- a/feedback-reports/Front-end_Dev_with_React_and_GenAI_Advanced_Program.xlsx
+++ b/feedback-reports/Front-end_Dev_with_React_and_GenAI_Advanced_Program.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="14_{3042AF75-6E86-424F-8407-3C349A2A67E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3AB3B84A-7847-4627-A5BA-D2B410734FBB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{3042AF75-6E86-424F-8407-3C349A2A67E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="119">
   <si>
     <t>Program Name:</t>
   </si>
@@ -180,7 +180,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Replace with:
@@ -192,7 +191,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Responsive Web Design &amp; User Experience
@@ -203,7 +201,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create visually appealing and responsive web interfaces by structuring content effectively and applying modern styling practices aligned with UI/UX principles.
@@ -215,7 +212,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Interactive Web Development &amp; API Integration
@@ -226,7 +222,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build dynamic, interactive web applications by handling user interactions and seamlessly connecting front-end interfaces with backend services through APIs.</t>
@@ -283,7 +278,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Replace with below:
@@ -295,7 +289,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Component-Based UI Development
@@ -306,7 +299,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build reusable and maintainable user interfaces using JSX, components, and props.
@@ -318,7 +310,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> State, Interactivity &amp; Data Handling
@@ -329,7 +320,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Create dynamic apps by managing state, handling interactions, and integrating APIs with React hooks.
@@ -341,7 +331,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Scalable, Styled &amp; Tested Apps
@@ -352,7 +341,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Improve reliability with TypeScript, design responsive UIs using Material UI, and ensure quality through testing using Jest and RTL.</t>
@@ -394,7 +382,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Replace with below content:
@@ -406,7 +393,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Forms &amp; Navigation in React Applications
@@ -417,7 +403,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Build and validate complex forms and enable seamless user journeys through efficient form handling and in-app routing.
@@ -429,7 +414,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Authentication, State Management &amp; Performance
@@ -440,7 +424,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Implement secure access control and manage application state effectively using Context API while optimizing performance for production-ready apps.</t>
@@ -554,7 +537,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Add with:
 • </t>
@@ -565,7 +547,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">SQL Querying &amp; Data Operations
 </t>
@@ -575,7 +556,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Build strong hands-on skills to retrieve, analyze, and manipulate data using SQL, enabling you to extract meaningful insights and work effectively with real-world datasets.
 • </t>
@@ -586,7 +566,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Database Design, Integrity &amp; Advanced Capabilities
 </t>
@@ -596,7 +575,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>Design structured databases using ER diagrams and define robust schemas while ensuring data consistency, and extend functionality through automation and support for modern data formats.</t>
     </r>
@@ -613,7 +591,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Add with : 
 1)</t>
@@ -624,7 +601,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Core Java Programming &amp; Problem Solving
 </t>
@@ -634,7 +610,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Apply Core Java fundamentals—variables, control flow, arrays, strings, recursion, and searching/sorting—to build efficient, program logic.
 2) </t>
@@ -645,7 +620,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Object-Oriented Application Development
 </t>
@@ -655,7 +629,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Apply object-oriented concepts and exception handling to design well-structured Java applications.</t>
     </r>
@@ -672,7 +645,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Add with :
@@ -684,7 +656,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">• Data Structures Implementation
@@ -695,7 +666,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Implement core data structures such as arrays, stacks, queues, linked lists, trees, and hash tables along with searching and sorting algorithms.
@@ -707,7 +677,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Algorithm Analysis and Optimization
@@ -718,7 +687,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Analyse time and space complexity and apply recursion and suitable data structures to solve performance-critical problems.</t>
@@ -736,7 +704,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add with:
@@ -748,7 +715,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Testing and Collections
@@ -759,7 +725,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Write unit tests and manage data using collections and generics for organized, reliable programs.
@@ -771,7 +736,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Modern Java Practices
@@ -782,7 +746,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Apply functional programming features to write concise, efficient code for data processing.</t>
@@ -818,9 +781,6 @@
 5. HostelBites Lite – Smart Mess Manager — Build a responsive React + TypeScript app using components, state, and hooks to manage meal preferences and demand insights.
 6. MovieMate – Personal Watchlist — Build a React SPA to explore, filter, and manage a personalized movie watchlist using routing, forms, global state, and performance optimizations.</t>
     </r>
-  </si>
-  <si>
-    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -840,18 +800,15 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -859,34 +816,29 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -901,7 +853,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -953,7 +904,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -976,23 +927,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1028,12 +968,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1348,7 +1282,6 @@
     <col min="5" max="5" width="40" style="2" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
     <col min="7" max="7" width="58.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1367,8 +1300,8 @@
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1382,11 +1315,11 @@
       <c r="D2" s="4"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1406,9 +1339,6 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1431,8 +1361,7 @@
       <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -1495,7 +1424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="179.4" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1514,7 +1443,7 @@
       <c r="F8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2061,6 +1990,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008081BF50E816F94B87E854E2907183B0" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6f57204d0cc9b1c65f7ab94eaa7dcc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b8ad293-1655-4b1e-95cd-578b981aff66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed196dee19b1527225c6137bc92e865" ns2:_="">
     <xsd:import namespace="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
@@ -2222,12 +2157,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2238,6 +2167,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2BB2AD3-7CBE-41F4-9CD2-29EEE306E664}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{730B4967-9014-486D-BC0B-FED06405060C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2255,22 +2200,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2BB2AD3-7CBE-41F4-9CD2-29EEE306E664}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30BD62A0-3FD1-4B18-9B85-9BA10240F7E5}">
   <ds:schemaRefs>
